--- a/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_long.xlsx
+++ b/processed-data/21_Xenium/02_xenium_compile_custom/ERC_Xenium_ALL_probes_long.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F544"/>
+  <dimension ref="A1:F543"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -438,6 +438,9 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -491,6 +494,9 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -679,6 +685,9 @@
       <c r="E12" t="b">
         <v>1</v>
       </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -704,6 +713,9 @@
       <c r="E13" t="b">
         <v>1</v>
       </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -752,6 +764,9 @@
       <c r="E15" t="b">
         <v>1</v>
       </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -777,6 +792,9 @@
       <c r="E16" t="b">
         <v>1</v>
       </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -797,6 +815,9 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1097,6 +1118,9 @@
       <c r="E28" t="b">
         <v>1</v>
       </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1145,6 +1169,9 @@
       <c r="E30" t="b">
         <v>1</v>
       </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1198,6 +1225,9 @@
       <c r="E32" t="b">
         <v>1</v>
       </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1240,12 +1270,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Oligo.5 specific MR genes - Oligo.5/Oligo.2: 2.851, Oligo.5 specific Enrich genes t= 12.26</t>
+          <t>globl MR genes -  Oligo.5/Excit.L2_5.2: 1.322</t>
         </is>
       </c>
       <c r="E34" t="b">
@@ -1258,51 +1288,54 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ATP10A</t>
+          <t>ARHGEF3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.5</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_up</t>
+          <t>Oligo.5 specific MR genes - Oligo.5/Oligo.2: 2.851, Oligo.5 specific Enrich genes t= 12.26</t>
         </is>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ATP2C2</t>
+          <t>ATP10A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>DEG carrier top: Oligo.3 EA_up</t>
         </is>
       </c>
       <c r="E36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -1321,12 +1354,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.45</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="E37" t="b">
@@ -1339,22 +1372,22 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>B4GALNT1</t>
+          <t>ATP2C2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.45</t>
         </is>
       </c>
       <c r="E38" t="b">
@@ -1367,7 +1400,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCAN</t>
+          <t>B4GALNT1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1395,26 +1428,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCAS1</t>
+          <t>BCAN</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 8.31</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -1428,71 +1461,77 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WM.uf~Sp09D07</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SpD Enrich gene t=5.88</t>
+          <t>Astro.3 specific Enrich genes t= 8.31</t>
         </is>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMP6</t>
+          <t>BCAS1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>WM.uf~Sp09D07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>SpD Enrich gene t=5.88</t>
         </is>
       </c>
       <c r="E42" t="b">
         <v>0</v>
       </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BRINP3</t>
+          <t>BMP6</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="E43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -1501,12 +1540,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BTBD11</t>
+          <t>BRINP3</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1516,7 +1555,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E44" t="b">
@@ -1529,12 +1568,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C1QL3</t>
+          <t>BTBD11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Excit.L6_IT</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1544,7 +1583,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E45" t="b">
@@ -1557,12 +1596,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>C1orf162</t>
+          <t>C1QL3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L6_IT</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1572,7 +1611,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Excit.L6_IT</t>
         </is>
       </c>
       <c r="E46" t="b">
@@ -1585,51 +1624,54 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CABLES1</t>
+          <t>C1orf162</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CALCRL</t>
+          <t>CABLES1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -1643,17 +1685,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 3.293</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E49" t="b">
@@ -1671,42 +1713,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2_5.2: 3.293</t>
         </is>
       </c>
       <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAPG</t>
+          <t>CALCRL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E51" t="b">
@@ -1719,12 +1764,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAPN3</t>
+          <t>CAPG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1734,7 +1779,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E52" t="b">
@@ -1747,12 +1792,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAV1</t>
+          <t>CAPN3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1762,7 +1807,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E53" t="b">
@@ -1780,17 +1825,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 9.838</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E54" t="b">
@@ -1803,51 +1848,54 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CBS</t>
+          <t>CAV1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 9.838</t>
         </is>
       </c>
       <c r="E55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CCK</t>
+          <t>CBS</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="E56" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -1856,12 +1904,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CCL4</t>
+          <t>CCK</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1871,7 +1919,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E57" t="b">
@@ -1884,12 +1932,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CCL5</t>
+          <t>CCL4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1899,7 +1947,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E58" t="b">
@@ -1912,12 +1960,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CCNA1</t>
+          <t>CCL5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1927,7 +1975,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E59" t="b">
@@ -1940,7 +1988,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CCNB2</t>
+          <t>CCNA1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1968,12 +2016,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>CCNB2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1983,7 +2031,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="E61" t="b">
@@ -1996,7 +2044,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CD163</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2029,42 +2077,45 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>globl MR genes -  Macro/Micro.4: 20.131</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CD2</t>
+          <t>CD163</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>globl MR genes -  Macro/Micro.4: 20.131</t>
         </is>
       </c>
       <c r="E64" t="b">
@@ -2077,12 +2128,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CD36</t>
+          <t>CD2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2092,7 +2143,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E65" t="b">
@@ -2115,15 +2166,18 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L5_6_NP/Excit.L2: 2.702</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2140,12 +2194,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2: 2.702</t>
+          <t>globl MR genes -  Excit.L5_6_NP/Excit.L2: 2.702</t>
         </is>
       </c>
       <c r="E67" t="b">
@@ -2158,22 +2212,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CD3G</t>
+          <t>CD36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L2: 2.702</t>
         </is>
       </c>
       <c r="E68" t="b">
@@ -2186,7 +2240,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CD4</t>
+          <t>CD3G</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2214,7 +2268,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CD48</t>
+          <t>CD4</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2242,7 +2296,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CD52</t>
+          <t>CD48</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2270,7 +2324,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CD68</t>
+          <t>CD52</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2298,7 +2352,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CD83</t>
+          <t>CD68</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2326,12 +2380,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CD86</t>
+          <t>CD83</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2341,7 +2395,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E74" t="b">
@@ -2354,12 +2408,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CDH1</t>
+          <t>CD86</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2369,7 +2423,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E75" t="b">
@@ -2382,12 +2436,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CDH12</t>
+          <t>CDH1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2397,7 +2451,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E76" t="b">
@@ -2410,51 +2464,54 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CDH19</t>
+          <t>CDH12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E77" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CDH4</t>
+          <t>CDH19</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="E78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -2463,12 +2520,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CDH6</t>
+          <t>CDH4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2478,7 +2535,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E79" t="b">
@@ -2496,17 +2553,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 2.347</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E80" t="b">
@@ -2519,22 +2576,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CDK1</t>
+          <t>CDH6</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6b: 2.347</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -2547,12 +2604,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CEMIP</t>
+          <t>CDK1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2562,7 +2619,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -2585,15 +2642,18 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>globl MR genes -  Vasc.VLMC/Inhib.Pvalb: 5.829</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2605,17 +2665,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Excit.L5.1</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 1.978</t>
+          <t>globl MR genes -  Vasc.VLMC/Inhib.Pvalb: 5.829</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -2633,42 +2693,45 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5.1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_up</t>
+          <t>Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 1.978</t>
         </is>
       </c>
       <c r="E85" t="b">
+        <v>1</v>
+      </c>
+      <c r="F85" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CEMIP2</t>
+          <t>CEMIP</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>DEG carrier top: Oligo.3 EA_up</t>
         </is>
       </c>
       <c r="E86" t="b">
@@ -2686,17 +2749,17 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.594</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E87" t="b">
@@ -2709,22 +2772,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CENPF</t>
+          <t>CEMIP2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L6b: 1.594</t>
         </is>
       </c>
       <c r="E88" t="b">
@@ -2737,12 +2800,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CHODL</t>
+          <t>CENPF</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2752,7 +2815,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="E89" t="b">
@@ -2765,76 +2828,82 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CHRM3</t>
+          <t>CHN1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.3</t>
+          <t>SpD pw gene t=8.2</t>
         </is>
       </c>
       <c r="E90" t="b">
         <v>0</v>
       </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CHST11</t>
+          <t>CHODL</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.82</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E91" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>CLDN11</t>
+          <t>CHRM3</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>mediation gene: mediator Astro.3</t>
         </is>
       </c>
       <c r="E92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -2843,26 +2912,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CNDP1</t>
+          <t>CHST11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.82</t>
         </is>
       </c>
       <c r="E93" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -2871,25 +2940,28 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CNDP1</t>
+          <t>CLDN11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DEG carrier included: Astro.3 down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2901,20 +2973,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2926,7 +3001,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2936,32 +3011,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DEG carrier included: Inhib.Vip down</t>
+          <t>DEG carrier included: Astro.3 down</t>
         </is>
       </c>
       <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>CNTN2</t>
+          <t>CNDP1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -2974,26 +3052,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>CNTNAP2</t>
+          <t>CNDP1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
+          <t>DEG carrier included: Inhib.Vip down</t>
         </is>
       </c>
       <c r="E98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -3002,12 +3080,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>CNTNAP3B</t>
+          <t>CNTN2</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3017,7 +3095,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -3030,12 +3108,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>CNTNAP3B</t>
+          <t>CNTNAP2</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3045,11 +3123,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.2: 1.055</t>
         </is>
       </c>
       <c r="E100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -3058,12 +3136,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>COL12A1</t>
+          <t>CNTNAP3B</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3073,7 +3151,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="E101" t="b">
@@ -3086,12 +3164,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>COL12A1</t>
+          <t>CNTNAP3B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Excit.L2_5.2</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3101,7 +3179,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
+          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 1.699</t>
         </is>
       </c>
       <c r="E102" t="b">
@@ -3114,26 +3192,26 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>COL16A1</t>
+          <t>COL12A1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -3142,51 +3220,54 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>COL21A1</t>
+          <t>COL12A1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.79</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.016</t>
         </is>
       </c>
       <c r="E104" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>COL25A1</t>
+          <t>COL16A1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.061</t>
         </is>
       </c>
       <c r="E105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -3195,72 +3276,78 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>COL25A1</t>
+          <t>COL21A1</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.79</t>
         </is>
       </c>
       <c r="E106" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>COPS9</t>
+          <t>COL25A1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
+          <t>Base probe - Inhib.Sst</t>
         </is>
       </c>
       <c r="E107" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CORO1A</t>
+          <t>COL25A1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>globl MR genes -  Inhib.Sst/Inhib.Lamp5_Lhx6: 1.643</t>
         </is>
       </c>
       <c r="E108" t="b">
@@ -3273,37 +3360,40 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CPNE4</t>
+          <t>COPS9</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 up logFC=1.87</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/Inhib~Sp09D09: 1.112</t>
         </is>
       </c>
       <c r="E109" t="b">
         <v>0</v>
       </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CRHBP</t>
+          <t>CORO1A</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3313,7 +3403,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E110" t="b">
@@ -3326,26 +3416,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>CRYM</t>
+          <t>CPNE4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>DEG of interest: Oligo.3 up logFC=1.87</t>
         </is>
       </c>
       <c r="E111" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
@@ -3354,22 +3444,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CRYM</t>
+          <t>CRHBP</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.121, Excit.L5_6_NP specific Enrich genes t= 11.41</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="E112" t="b">
@@ -3382,12 +3472,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CSPG4</t>
+          <t>CRYM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3397,7 +3487,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -3410,22 +3500,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CTNNA3</t>
+          <t>CRYM</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 2.121, Excit.L5_6_NP specific Enrich genes t= 11.41</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -3438,22 +3528,22 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CTNNA3</t>
+          <t>CSPG4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 7.63</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -3466,12 +3556,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>CTNNA3</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3481,7 +3571,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -3494,22 +3584,22 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>CTSS</t>
+          <t>CTNNA3</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Astro.3 specific Enrich genes t= 7.63</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -3522,12 +3612,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CUX2</t>
+          <t>CTSH</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Excit.L2_3_IT</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3537,7 +3627,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L2_3_IT</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E118" t="b">
@@ -3550,7 +3640,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>CX3CR1</t>
+          <t>CTSS</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3578,12 +3668,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CXCL14</t>
+          <t>CUX2</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3593,7 +3683,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="E120" t="b">
@@ -3606,7 +3696,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CXCR4</t>
+          <t>CX3CR1</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3634,12 +3724,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CYTIP</t>
+          <t>CXCL14</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3649,7 +3739,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E122" t="b">
@@ -3662,37 +3752,40 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CYTIP</t>
+          <t>CXCR4</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Oligo.5</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.5 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E123" t="b">
+        <v>1</v>
+      </c>
+      <c r="F123" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>DCN</t>
+          <t>CYTIP</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3702,7 +3795,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E124" t="b">
@@ -3715,22 +3808,22 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>DDR2</t>
+          <t>CYTIP</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Oligo.5</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>DEG carrier included: Oligo.5 up</t>
         </is>
       </c>
       <c r="E125" t="b">
@@ -3743,12 +3836,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>DNER</t>
+          <t>DCN</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3758,7 +3851,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E126" t="b">
@@ -3771,22 +3864,22 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DNER</t>
+          <t>DDR2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Astro.4</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Astro.4 specific MR gene - Astro.4/Astro.1: 1.855</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -3804,17 +3897,17 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Inhib.Lamp5</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.516</t>
+          <t>Base probe - Inhib.Lamp5</t>
         </is>
       </c>
       <c r="E128" t="b">
@@ -3832,67 +3925,73 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Inhib~Sp09D09</t>
+          <t>Astro.4</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: Inhib~Sp09D09/L5~Sp09D03: 1.798, SpD Enrich gene t=14.7</t>
+          <t>Astro.4 specific MR gene - Astro.4/Astro.1: 1.855</t>
         </is>
       </c>
       <c r="E129" t="b">
+        <v>1</v>
+      </c>
+      <c r="F129" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DVL2</t>
+          <t>DNER</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.516</t>
         </is>
       </c>
       <c r="E130" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F130" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EFHD1</t>
+          <t>DNER</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Inhib~Sp09D09</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>SpD MeanRatio gene: Inhib~Sp09D09/L5~Sp09D03: 1.798, SpD Enrich gene t=14.7</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -3905,26 +4004,26 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>EGFR</t>
+          <t>DVL2</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="E132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
@@ -3933,12 +4032,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ELOVL2</t>
+          <t>EFHD1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3948,7 +4047,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -3961,57 +4060,63 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENC1</t>
+          <t>EGFR</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E134" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F134" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ENSG00000286293</t>
+          <t>ELOVL2</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_down</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E135" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F135" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ENSG00000286438</t>
+          <t>ENC1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4021,41 +4126,47 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 EA_down</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E136" t="b">
         <v>0</v>
       </c>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ENSG00000289591</t>
+          <t>ERBB3</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E137" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F137" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -4066,17 +4177,17 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E138" t="b">
@@ -4099,15 +4210,18 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E139" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4124,66 +4238,72 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="E140" t="b">
+        <v>1</v>
+      </c>
+      <c r="F140" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ERBB3</t>
+          <t>ERBB4</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>Oligo.1 specific Enrich genes t= 5.58</t>
         </is>
       </c>
       <c r="E141" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ERBB4</t>
+          <t>ERMN</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Oligo.1 specific Enrich genes t= 5.58</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -4197,17 +4317,17 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>WM~Sp09D06</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59</t>
         </is>
       </c>
       <c r="E143" t="b">
@@ -4225,20 +4345,23 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>WM~Sp09D06</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: WM~Sp09D06/L6~Sp09D04: 4.59</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E144" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4250,7 +4373,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4260,10 +4383,13 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>DEG carrier included: Inhib.Vip down</t>
         </is>
       </c>
       <c r="E145" t="b">
+        <v>1</v>
+      </c>
+      <c r="F145" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4275,71 +4401,77 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>DEG carrier included: Inhib.Vip down</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E146" t="b">
+        <v>1</v>
+      </c>
+      <c r="F146" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ERMN</t>
+          <t>EXOC7</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>OPC.5 specific Enrich genes t= 7.33</t>
         </is>
       </c>
       <c r="E147" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>EXOC7</t>
+          <t>EYA4</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>OPC.5 specific Enrich genes t= 7.33</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -4358,12 +4490,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
         </is>
       </c>
       <c r="E149" t="b">
@@ -4376,51 +4508,54 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>EYA4</t>
+          <t>FAM171B</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Lamp5_Lhx6/Oligo.2: 6.508</t>
+          <t>Astro.1 specific Enrich genes t= 8.3</t>
         </is>
       </c>
       <c r="E150" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FAM171B</t>
+          <t>FASLG</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Astro.1 specific Enrich genes t= 8.3</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E151" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -4429,12 +4564,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>FASLG</t>
+          <t>FBLN1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4444,7 +4579,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E152" t="b">
@@ -4462,17 +4597,17 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
         </is>
       </c>
       <c r="E153" t="b">
@@ -4485,32 +4620,35 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FBLN1</t>
+          <t>FCER1G</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down-EA_up*</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E154" t="b">
+        <v>1</v>
+      </c>
+      <c r="F154" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>FCER1G</t>
+          <t>FCGR1A</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4538,7 +4676,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>FCGR1A</t>
+          <t>FCGR3A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4566,12 +4704,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>FCGR3A</t>
+          <t>FGFR2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4581,7 +4719,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E157" t="b">
@@ -4594,12 +4732,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>FGFR2</t>
+          <t>FGFR3</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4609,7 +4747,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E158" t="b">
@@ -4622,26 +4760,26 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>FGFR3</t>
+          <t>FIGN</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
         </is>
       </c>
       <c r="E159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -4650,26 +4788,26 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>FIGN</t>
+          <t>FILIP1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.143</t>
+          <t>Base probe - Excit.L6_CT</t>
         </is>
       </c>
       <c r="E160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -4678,12 +4816,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FILIP1</t>
+          <t>FLT1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4693,7 +4831,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_CT</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E161" t="b">
@@ -4706,26 +4844,26 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FLT1</t>
+          <t>FOS</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>DEG carrier top: Oligo.3 up logFC=2.77, DEG of interest: Oligo.3 up logFC=2.77</t>
         </is>
       </c>
       <c r="E162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -4734,51 +4872,54 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FOS</t>
+          <t>FSTL4</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 up logFC=2.77, DEG of interest: Oligo.3 up logFC=2.77</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="E163" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>FSTL4</t>
+          <t>FZD8</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="E164" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" t="b">
         <v>1</v>
@@ -4787,26 +4928,29 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FZD8</t>
+          <t>GAD1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E165" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F165" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -4817,17 +4961,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Inhib~Sp09D09</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -4845,20 +4989,23 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Inhib~Sp09D09</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.35, SpD Enrich gene t=17.85</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E167" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4875,40 +5022,46 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E168" t="b">
+        <v>1</v>
+      </c>
+      <c r="F168" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>GAD1</t>
+          <t>GAD2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E169" t="b">
+        <v>1</v>
+      </c>
+      <c r="F169" t="b">
         <v>1</v>
       </c>
     </row>
@@ -4920,17 +5073,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Inhib~Sp09D09</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34</t>
         </is>
       </c>
       <c r="E170" t="b">
@@ -4948,57 +5101,63 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Inhib~Sp09D09</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: Inhib~Sp09D09/LD~Sp09D02: 3.308, SpD Enrich gene t=15.34</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E171" t="b">
+        <v>1</v>
+      </c>
+      <c r="F171" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>GAD2</t>
+          <t>GAS2L3</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E172" t="b">
+        <v>1</v>
+      </c>
+      <c r="F172" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>GAS2L3</t>
+          <t>GJA1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5008,7 +5167,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E173" t="b">
@@ -5026,17 +5185,17 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>L1~Sp09D05</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
         </is>
       </c>
       <c r="E174" t="b">
@@ -5049,25 +5208,28 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>GJA1</t>
+          <t>GNA14-AS1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>L1~Sp09D05</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: L1~Sp09D05/LD~Sp09D02: 1.387</t>
+          <t>globl MR genes -  Astro.1/Astro.3: 1.372</t>
         </is>
       </c>
       <c r="E175" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5145,12 +5307,15 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>DEG carrier top: Excit.L5.2 up</t>
         </is>
       </c>
       <c r="E178" t="b">
         <v>0</v>
       </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5204,6 +5369,9 @@
       <c r="E180" t="b">
         <v>0</v>
       </c>
+      <c r="F180" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5257,6 +5425,9 @@
       <c r="E182" t="b">
         <v>0</v>
       </c>
+      <c r="F182" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5394,6 +5565,9 @@
       <c r="E187" t="b">
         <v>0</v>
       </c>
+      <c r="F187" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5447,6 +5621,9 @@
       <c r="E189" t="b">
         <v>1</v>
       </c>
+      <c r="F189" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6032,6 +6209,9 @@
       <c r="E210" t="b">
         <v>1</v>
       </c>
+      <c r="F210" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6057,6 +6237,9 @@
       <c r="E211" t="b">
         <v>1</v>
       </c>
+      <c r="F211" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6082,6 +6265,9 @@
       <c r="E212" t="b">
         <v>1</v>
       </c>
+      <c r="F212" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6107,6 +6293,9 @@
       <c r="E213" t="b">
         <v>0</v>
       </c>
+      <c r="F213" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6132,6 +6321,9 @@
       <c r="E214" t="b">
         <v>0</v>
       </c>
+      <c r="F214" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6325,6 +6517,9 @@
       <c r="E221" t="b">
         <v>1</v>
       </c>
+      <c r="F221" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6350,6 +6545,9 @@
       <c r="E222" t="b">
         <v>1</v>
       </c>
+      <c r="F222" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6403,6 +6601,9 @@
       <c r="E224" t="b">
         <v>0</v>
       </c>
+      <c r="F224" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6568,6 +6769,9 @@
       <c r="E230" t="b">
         <v>1</v>
       </c>
+      <c r="F230" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6817,6 +7021,9 @@
       <c r="E239" t="b">
         <v>1</v>
       </c>
+      <c r="F239" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6870,6 +7077,9 @@
       <c r="E241" t="b">
         <v>1</v>
       </c>
+      <c r="F241" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6895,6 +7105,9 @@
       <c r="E242" t="b">
         <v>0</v>
       </c>
+      <c r="F242" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6948,6 +7161,9 @@
       <c r="E244" t="b">
         <v>0</v>
       </c>
+      <c r="F244" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -6967,12 +7183,15 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 up</t>
+          <t>DEG carrier top: Excit.L5.2 up</t>
         </is>
       </c>
       <c r="E245" t="b">
         <v>0</v>
       </c>
+      <c r="F245" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7026,6 +7245,9 @@
       <c r="E247" t="b">
         <v>0</v>
       </c>
+      <c r="F247" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7051,6 +7273,9 @@
       <c r="E248" t="b">
         <v>0</v>
       </c>
+      <c r="F248" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7104,6 +7329,9 @@
       <c r="E250" t="b">
         <v>0</v>
       </c>
+      <c r="F250" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7207,36 +7435,39 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L2_5.1 down</t>
+          <t>DEG carrier top: Excit.L2_5.1 down</t>
         </is>
       </c>
       <c r="E254" t="b">
         <v>0</v>
       </c>
+      <c r="F254" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>LRRK1</t>
+          <t>LRRC63</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>globl MR genes -  Oligo.2/Oligo.1: 1.457</t>
         </is>
       </c>
       <c r="E255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F255" t="b">
         <v>1</v>
@@ -7245,12 +7476,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>LRRK2</t>
+          <t>LRRK1</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -7260,7 +7491,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E256" t="b">
@@ -7278,20 +7509,23 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up, DEG of interest: Oligo.3 up logFC=1.61</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E257" t="b">
+        <v>1</v>
+      </c>
+      <c r="F257" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7308,22 +7542,25 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 up, DEG of interest: Oligo.3 up logFC=1.61</t>
         </is>
       </c>
       <c r="E258" t="b">
+        <v>1</v>
+      </c>
+      <c r="F258" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>LURAP1L-AS1</t>
+          <t>LRRK2</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7333,41 +7570,44 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 down logFC=-1.48</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E259" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F259" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>LY86</t>
+          <t>LURAP1L-AS1</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier top: Oligo.3 down logFC=-1.48</t>
         </is>
       </c>
       <c r="E260" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F260" t="b">
         <v>1</v>
@@ -7376,12 +7616,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>LYPD6</t>
+          <t>LY86</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -7391,7 +7631,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E261" t="b">
@@ -7404,12 +7644,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>LYPD6B</t>
+          <t>LYPD6</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Inhib.Sncg</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -7419,7 +7659,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E262" t="b">
@@ -7432,12 +7672,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>LYVE1</t>
+          <t>LYPD6B</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Inhib.Sncg</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -7447,7 +7687,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Inhib.Sncg</t>
         </is>
       </c>
       <c r="E263" t="b">
@@ -7465,42 +7705,45 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>globl MR genes -  Macro/Micro.4: 2.653</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E264" t="b">
+        <v>1</v>
+      </c>
+      <c r="F264" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>LYVE1</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>globl MR genes -  Macro/Micro.4: 2.653</t>
         </is>
       </c>
       <c r="E265" t="b">
@@ -7518,20 +7761,23 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.77</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E266" t="b">
+        <v>1</v>
+      </c>
+      <c r="F266" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7548,22 +7794,25 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.77</t>
         </is>
       </c>
       <c r="E267" t="b">
+        <v>1</v>
+      </c>
+      <c r="F267" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>MAGED2</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7573,41 +7822,44 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E268" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F268" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>MAL</t>
+          <t>MAGED2</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="E269" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -7621,27 +7873,30 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.76</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E270" t="b">
+        <v>1</v>
+      </c>
+      <c r="F270" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>MAPT</t>
+          <t>MAL</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7656,37 +7911,43 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 down logFC=-0.56</t>
+          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.76</t>
         </is>
       </c>
       <c r="E271" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F271" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>MBP</t>
+          <t>MAPT</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>WM.uf~Sp09D07</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>SpD Enrich gene t=6.53</t>
+          <t>DEG of interest: Oligo.3 down logFC=-0.56</t>
         </is>
       </c>
       <c r="E272" t="b">
         <v>0</v>
       </c>
+      <c r="F272" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7696,22 +7957,25 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>WM.uf~Sp09D07</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 down logFC=-0.69</t>
+          <t>SpD Enrich gene t=6.53</t>
         </is>
       </c>
       <c r="E273" t="b">
         <v>0</v>
       </c>
+      <c r="F273" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7726,41 +7990,44 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG of interest: Oligo.3 down logFC=-0.69</t>
         </is>
       </c>
       <c r="E274" t="b">
         <v>0</v>
       </c>
+      <c r="F274" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>MCTP2</t>
+          <t>MBP</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E275" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F275" t="b">
         <v>1</v>
@@ -7774,20 +8041,23 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L6b/Vasc.VLMC: 3.051</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E276" t="b">
+        <v>1</v>
+      </c>
+      <c r="F276" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7804,12 +8074,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L5_6_NP: 5.834</t>
+          <t>globl MR genes -  Excit.L6b/Vasc.VLMC: 3.051</t>
         </is>
       </c>
       <c r="E277" t="b">
@@ -7822,12 +8092,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>MEG3</t>
+          <t>MCTP2</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>OPC.5</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7837,11 +8107,11 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.019</t>
+          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L5_6_NP: 5.834</t>
         </is>
       </c>
       <c r="E278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -7850,26 +8120,26 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>MEIS2</t>
+          <t>MEG3</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>OPC.5</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>OPC.5 specific MR genes - OPC.5/OPC.2: 1.019</t>
         </is>
       </c>
       <c r="E279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F279" t="b">
         <v>1</v>
@@ -7878,12 +8148,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MEPE</t>
+          <t>MEIS2</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7893,7 +8163,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E280" t="b">
@@ -7906,12 +8176,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MGST1</t>
+          <t>MEPE</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7921,7 +8191,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E281" t="b">
@@ -7939,17 +8209,17 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.869</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E282" t="b">
@@ -7967,20 +8237,23 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.869</t>
         </is>
       </c>
       <c r="E283" t="b">
+        <v>1</v>
+      </c>
+      <c r="F283" t="b">
         <v>1</v>
       </c>
     </row>
@@ -7997,22 +8270,25 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E284" t="b">
+        <v>1</v>
+      </c>
+      <c r="F284" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>MIAT</t>
+          <t>MGST1</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -8022,41 +8298,44 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_up</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E285" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F285" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>MKI67</t>
+          <t>MIAT</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>DEG carrier top: Oligo.3 AA_up</t>
         </is>
       </c>
       <c r="E286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F286" t="b">
         <v>1</v>
@@ -8065,26 +8344,26 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>MMD2</t>
+          <t>MKI67</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.004</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="E287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="b">
         <v>1</v>
@@ -8093,26 +8372,26 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>MOBP</t>
+          <t>MMD2</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.004</t>
         </is>
       </c>
       <c r="E288" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F288" t="b">
         <v>1</v>
@@ -8126,20 +8405,23 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>WM.uf~Sp09D07</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>SpD Enrich gene t=6.03</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E289" t="b">
+        <v>1</v>
+      </c>
+      <c r="F289" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8151,7 +8433,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>WM~Sp09D06</t>
+          <t>WM.uf~Sp09D07</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -8161,10 +8443,13 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: WM~Sp09D06/WM.uf~Sp09D07: 3.219</t>
+          <t>SpD Enrich gene t=6.03</t>
         </is>
       </c>
       <c r="E290" t="b">
+        <v>1</v>
+      </c>
+      <c r="F290" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8176,42 +8461,45 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>WM~Sp09D06</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>DEG carrier included: Astro.2 down</t>
+          <t>SpD MeanRatio gene: WM~Sp09D06/WM.uf~Sp09D07: 3.219</t>
         </is>
       </c>
       <c r="E291" t="b">
+        <v>1</v>
+      </c>
+      <c r="F291" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>MOG</t>
+          <t>MOBP</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="E292" t="b">
@@ -8224,12 +8512,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>MOG</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -8239,7 +8527,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E293" t="b">
@@ -8257,46 +8545,49 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>globl MR genes -  Macro/Micro.3: 4.29</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E294" t="b">
+        <v>1</v>
+      </c>
+      <c r="F294" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>MT-CO3</t>
+          <t>MS4A6A</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141</t>
+          <t>globl MR genes -  Macro/Micro.3: 4.29</t>
         </is>
       </c>
       <c r="E295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="b">
         <v>1</v>
@@ -8305,12 +8596,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MT-CYB</t>
+          <t>MT-CO3</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -8320,7 +8611,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.175</t>
+          <t>Oligo.3 specific MR genes - Oligo.3/Oligo.4: 1.141</t>
         </is>
       </c>
       <c r="E296" t="b">
@@ -8333,22 +8624,22 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>MT-ND1</t>
+          <t>MT-CO3</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.201</t>
+          <t>DEG carrier top: Excit.L5.2 down</t>
         </is>
       </c>
       <c r="E297" t="b">
@@ -8361,37 +8652,40 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MT-ND4</t>
+          <t>MT-CYB</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
+          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.175</t>
         </is>
       </c>
       <c r="E298" t="b">
         <v>0</v>
       </c>
+      <c r="F298" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MTX2</t>
+          <t>MT-ND1</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -8401,7 +8695,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Oligo.2 specific Enrich genes t= 11.38</t>
+          <t>Excit.L2_5.1 specific MR genes - Excit.L2_5.1/Excit.L6b: 1.201</t>
         </is>
       </c>
       <c r="E299" t="b">
@@ -8414,26 +8708,26 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MYO16</t>
+          <t>MTX2</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Oligo.2</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>Oligo.2 specific Enrich genes t= 11.38</t>
         </is>
       </c>
       <c r="E300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F300" t="b">
         <v>1</v>
@@ -8442,12 +8736,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MYO5B</t>
+          <t>MYO16</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -8457,7 +8751,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E301" t="b">
@@ -8480,37 +8774,40 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E302" t="b">
+        <v>1</v>
+      </c>
+      <c r="F302" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>MYRF</t>
+          <t>MYO5B</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>globl MR genes -  Inhib.Pvalb/Inhib.Sst: 2.178</t>
         </is>
       </c>
       <c r="E303" t="b">
@@ -8523,51 +8820,54 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>NAP1L3</t>
+          <t>MYRF</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E304" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F304" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>NCSTN</t>
+          <t>NAP1L3</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F305" t="b">
         <v>1</v>
@@ -8576,12 +8876,12 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>NDST4</t>
+          <t>NCSTN</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -8591,7 +8891,7 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E306" t="b">
@@ -8609,17 +8909,17 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="E307" t="b">
@@ -8632,22 +8932,22 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>NES</t>
+          <t>NDST4</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L5.1: 3.841</t>
         </is>
       </c>
       <c r="E308" t="b">
@@ -8660,51 +8960,54 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>NETO1</t>
+          <t>NES</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.2</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E309" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F309" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>NKG7</t>
+          <t>NETO1</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>mediation gene: mediator Astro.2</t>
         </is>
       </c>
       <c r="E310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F310" t="b">
         <v>1</v>
@@ -8713,51 +9016,54 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>NLGN1</t>
+          <t>NKG7</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E311" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F311" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>NNAT</t>
+          <t>NLGN1</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN1 -&gt; NRXN3,NRXN1 -&gt; NLGN1,NRXN3 -&gt; NLGN1</t>
         </is>
       </c>
       <c r="E312" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312" t="b">
         <v>1</v>
@@ -8771,17 +9077,17 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E313" t="b">
@@ -8799,42 +9105,45 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>L6~Sp09D04</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
+          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L6_CT: 1.661</t>
         </is>
       </c>
       <c r="E314" t="b">
+        <v>1</v>
+      </c>
+      <c r="F314" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>NOTCH1</t>
+          <t>NNAT</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>L6~Sp09D04</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>SpD MeanRatio gene: L6~Sp09D04/L2.3~Sp09D01: 1.542, SpD Enrich gene t=10.01</t>
         </is>
       </c>
       <c r="E315" t="b">
@@ -8847,12 +9156,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>NPFFR2</t>
+          <t>NOTCH1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -8862,7 +9171,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E316" t="b">
@@ -8880,20 +9189,23 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469</t>
+          <t>Base probe - Excit.L6b</t>
         </is>
       </c>
       <c r="E317" t="b">
+        <v>1</v>
+      </c>
+      <c r="F317" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8910,12 +9222,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
+          <t>globl MR genes -  Excit.L6_CT/Excit.L2_5.1: 3.469</t>
         </is>
       </c>
       <c r="E318" t="b">
@@ -8928,22 +9240,22 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>NPNT</t>
+          <t>NPFFR2</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2_5.1: 3.469</t>
         </is>
       </c>
       <c r="E319" t="b">
@@ -8966,15 +9278,18 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="E320" t="b">
+        <v>1</v>
+      </c>
+      <c r="F320" t="b">
         <v>1</v>
       </c>
     </row>
@@ -8986,17 +9301,17 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
+          <t>globl MR genes -  Inhib.Chandelier/Excit.L2_5.2: 3.131</t>
         </is>
       </c>
       <c r="E321" t="b">
@@ -9009,51 +9324,54 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>NPTXR</t>
+          <t>NPNT</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Excit.L2_5.2</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5_6_NP: 6.062</t>
         </is>
       </c>
       <c r="E322" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F322" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>NPY1R</t>
+          <t>NPTXR</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="E323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F323" t="b">
         <v>1</v>
@@ -9062,12 +9380,12 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>NR2F2</t>
+          <t>NPY1R</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -9077,7 +9395,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E324" t="b">
@@ -9090,12 +9408,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>NR4A2</t>
+          <t>NR2F2</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -9105,7 +9423,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E325" t="b">
@@ -9123,27 +9441,30 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E326" t="b">
+        <v>1</v>
+      </c>
+      <c r="F326" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>NRG3</t>
+          <t>NR4A2</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -9153,41 +9474,44 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E327" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F327" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>NRP1</t>
+          <t>NRG3</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>DEG LR interactions: NRG3 -&gt; ERBB3</t>
         </is>
       </c>
       <c r="E328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F328" t="b">
         <v>1</v>
@@ -9201,17 +9525,17 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Excit.L6_CT</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E329" t="b">
@@ -9229,52 +9553,58 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Excit.L6_CT</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>DEG carrier included: Macro down</t>
+          <t>Excit.L6_CT specific MR gene - Excit.L6_CT/Excit.L2: 1.859</t>
         </is>
       </c>
       <c r="E330" t="b">
+        <v>1</v>
+      </c>
+      <c r="F330" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>NRXN1</t>
+          <t>NRP1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
+          <t>DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="E331" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F331" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>NRXN3</t>
+          <t>NRXN1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -9289,36 +9619,39 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN1,NLGN4X -&gt; NRXN1,NRXN1 -&gt; NLGN1,NXPH1 -&gt; NRXN1</t>
         </is>
       </c>
       <c r="E332" t="b">
         <v>0</v>
       </c>
+      <c r="F332" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>NTNG1</t>
+          <t>NRXN3</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>DEG LR interactions: NLGN1 -&gt; NRXN3,NRXN3 -&gt; NLGN1,NXPH1 -&gt; NRXN3</t>
         </is>
       </c>
       <c r="E333" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F333" t="b">
         <v>1</v>
@@ -9332,17 +9665,17 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Astro.4</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E334" t="b">
@@ -9355,22 +9688,22 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>NTNG2</t>
+          <t>NTNG1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.4</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Astro.4 specific MR gene - Astro.4/Astro.2: 2.001</t>
         </is>
       </c>
       <c r="E335" t="b">
@@ -9383,26 +9716,26 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>NTRK3</t>
+          <t>NTNG2</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>Oligo.3 specific Enrich genes t= 9.07</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" t="b">
         <v>1</v>
@@ -9421,41 +9754,44 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>DEG LR interactions: NTRK3 -&gt; PTPRD</t>
+          <t>Oligo.3 specific Enrich genes t= 9.07</t>
         </is>
       </c>
       <c r="E337" t="b">
         <v>0</v>
       </c>
+      <c r="F337" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>NWD2</t>
+          <t>NTRK3</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>DEG LR interactions: NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="E338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338" t="b">
         <v>1</v>
@@ -9464,12 +9800,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>NXPH2</t>
+          <t>NWD2</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -9479,7 +9815,7 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E339" t="b">
@@ -9497,17 +9833,17 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="E340" t="b">
@@ -9520,22 +9856,22 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>OLIG1</t>
+          <t>NXPH2</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 16.109</t>
         </is>
       </c>
       <c r="E341" t="b">
@@ -9548,7 +9884,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>OLIG2</t>
+          <t>OLIG1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -9581,42 +9917,45 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>OPC.4</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>globl MR genes -  OPC.4/OPC.1: 1.089</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E343" t="b">
+        <v>1</v>
+      </c>
+      <c r="F343" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>OPALIN</t>
+          <t>OLIG2</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>OPC.4</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>globl MR genes -  OPC.4/OPC.1: 1.089</t>
         </is>
       </c>
       <c r="E344" t="b">
@@ -9634,20 +9973,23 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.1/Oligo.4: 1.2</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E345" t="b">
+        <v>1</v>
+      </c>
+      <c r="F345" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9659,17 +10001,17 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific Enrich genes t= 7.46</t>
+          <t>globl MR genes -  Oligo.1/Oligo.4: 1.2</t>
         </is>
       </c>
       <c r="E346" t="b">
@@ -9687,7 +10029,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -9697,7 +10039,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2</t>
+          <t>Excit.L2_5.1 specific Enrich genes t= 7.46</t>
         </is>
       </c>
       <c r="E347" t="b">
@@ -9715,20 +10057,23 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>DEG carrier included: Astro.3 down</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.4: 1.2, Oligo.1 specific Enrich genes t= 5.2</t>
         </is>
       </c>
       <c r="E348" t="b">
+        <v>1</v>
+      </c>
+      <c r="F348" t="b">
         <v>1</v>
       </c>
     </row>
@@ -9740,7 +10085,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -9750,61 +10095,67 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.65</t>
+          <t>DEG carrier included: Astro.3 down</t>
         </is>
       </c>
       <c r="E349" t="b">
+        <v>1</v>
+      </c>
+      <c r="F349" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>OST4</t>
+          <t>OPALIN</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>LD~Sp09D02</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
+          <t>DEG carrier included: Oligo.3 down, DEG of interest: Oligo.3 down logFC=-0.65</t>
         </is>
       </c>
       <c r="E350" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F350" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>OTOGL</t>
+          <t>OST4</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>LD~Sp09D02</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>SpD MeanRatio gene: LD~Sp09D02/L2.3~Sp09D01: 1.109</t>
         </is>
       </c>
       <c r="E351" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F351" t="b">
         <v>1</v>
@@ -9813,12 +10164,12 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>P2RY12</t>
+          <t>OTOGL</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -9828,7 +10179,7 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="E352" t="b">
@@ -9846,42 +10197,45 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Macro</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>DEG carrier included: Macro down</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E353" t="b">
+        <v>1</v>
+      </c>
+      <c r="F353" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>P2RY13</t>
+          <t>P2RY12</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Macro</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>DEG carrier included: Macro down</t>
         </is>
       </c>
       <c r="E354" t="b">
@@ -9894,26 +10248,26 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>PABPN1</t>
+          <t>P2RY13</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F355" t="b">
         <v>1</v>
@@ -9927,7 +10281,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -9937,7 +10291,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific Enrich genes t= 9.16</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.1: 1.046</t>
         </is>
       </c>
       <c r="E356" t="b">
@@ -9950,26 +10304,26 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>PAX6</t>
+          <t>PABPN1</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Excit.L2_5.1 specific Enrich genes t= 9.16</t>
         </is>
       </c>
       <c r="E357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357" t="b">
         <v>1</v>
@@ -9978,26 +10332,26 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>PCDH9-AS2</t>
+          <t>PAX6</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F358" t="b">
         <v>1</v>
@@ -10006,26 +10360,26 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>PCNA</t>
+          <t>PCDH9-AS2</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Proliferation</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Base probe - Proliferation</t>
+          <t>Astro.1 specific MR genes - Astro.1/Astro.3: 1.486</t>
         </is>
       </c>
       <c r="E359" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F359" t="b">
         <v>1</v>
@@ -10034,12 +10388,12 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>PCSK1</t>
+          <t>PCNA</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Proliferation</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -10049,7 +10403,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>Base probe - Proliferation</t>
         </is>
       </c>
       <c r="E360" t="b">
@@ -10062,12 +10416,12 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>PCSK6</t>
+          <t>PCSK1</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -10077,7 +10431,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="E361" t="b">
@@ -10095,20 +10449,23 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E362" t="b">
+        <v>1</v>
+      </c>
+      <c r="F362" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10125,37 +10482,40 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E363" t="b">
+        <v>1</v>
+      </c>
+      <c r="F363" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>PDGFD</t>
+          <t>PCSK6</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5_Lhx6</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5_Lhx6</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E364" t="b">
@@ -10178,37 +10538,40 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
+          <t>Base probe - Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="E365" t="b">
+        <v>1</v>
+      </c>
+      <c r="F365" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>PDGFRA</t>
+          <t>PDGFD</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Inhib.Lamp5_Lhx6</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>globl MR genes -  Inhib.Lamp5_Lhx6/Excit.L2: 4.15</t>
         </is>
       </c>
       <c r="E366" t="b">
@@ -10221,12 +10584,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>PECAM1</t>
+          <t>PDGFRA</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -10236,7 +10599,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E367" t="b">
@@ -10249,12 +10612,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>PHLDB2</t>
+          <t>PECAM1</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -10264,7 +10627,7 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E368" t="b">
@@ -10277,7 +10640,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>PLCE1</t>
+          <t>PHLDB2</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -10310,17 +10673,17 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Astro.4</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 3.668</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E370" t="b">
@@ -10338,7 +10701,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Astro.4</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -10348,7 +10711,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023</t>
+          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 3.668</t>
         </is>
       </c>
       <c r="E371" t="b">
@@ -10366,42 +10729,45 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>DEG carrier included: Astro.2 down</t>
+          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L2_5.1: 4.023</t>
         </is>
       </c>
       <c r="E372" t="b">
+        <v>1</v>
+      </c>
+      <c r="F372" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>PLCH1</t>
+          <t>PLCE1</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Inhib.Sst</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst</t>
+          <t>DEG carrier included: Astro.2 down</t>
         </is>
       </c>
       <c r="E373" t="b">
@@ -10419,17 +10785,17 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2</t>
+          <t>Inhib.Sst</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
+          <t>Base probe - Inhib.Sst</t>
         </is>
       </c>
       <c r="E374" t="b">
@@ -10442,22 +10808,22 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>PLD5</t>
+          <t>PLCH1</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L2_5.2</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L5.1: 1.52</t>
         </is>
       </c>
       <c r="E375" t="b">
@@ -10470,26 +10836,26 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>PLP1</t>
+          <t>PLD5</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Excit.L2_5.1 specific Enrich genes t= 8.05</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F376" t="b">
         <v>1</v>
@@ -10503,71 +10869,77 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L2_5.1</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>DEG of interest: Oligo.3 down logFC=-0.93</t>
+          <t>Excit.L2_5.1 specific Enrich genes t= 8.05</t>
         </is>
       </c>
       <c r="E377" t="b">
         <v>0</v>
       </c>
+      <c r="F377" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>PLPPR4</t>
+          <t>PLP1</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Astro.1</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>mediation gene: mediator Astro.1</t>
+          <t>DEG of interest: Oligo.3 down logFC=-0.93</t>
         </is>
       </c>
       <c r="E378" t="b">
         <v>0</v>
       </c>
+      <c r="F378" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>POSTN</t>
+          <t>PLPPR4</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Astro.1</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>mediation gene: mediator Astro.1</t>
         </is>
       </c>
       <c r="E379" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F379" t="b">
         <v>1</v>
@@ -10576,12 +10948,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>POU6F2</t>
+          <t>POSTN</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10591,7 +10963,7 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E380" t="b">
@@ -10604,12 +10976,12 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PROX1</t>
+          <t>POU6F2</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Inhib.Sncg</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10619,7 +10991,7 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sncg</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="E381" t="b">
@@ -10637,42 +11009,45 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Inhib.Sncg</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
+          <t>Base probe - Inhib.Sncg</t>
         </is>
       </c>
       <c r="E382" t="b">
+        <v>1</v>
+      </c>
+      <c r="F382" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>PSEN1</t>
+          <t>PROX1</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>globl MR genes -  Inhib.Vip/Oligo.2: 1.345</t>
         </is>
       </c>
       <c r="E383" t="b">
@@ -10688,17 +11063,25 @@
           <t>PSEN1</t>
         </is>
       </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Oligo</t>
+        </is>
+      </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>OpenTargets AD gene</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E384" t="b">
+        <v>1</v>
+      </c>
+      <c r="F384" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10708,44 +11091,42 @@
           <t>PSEN1</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>Oligo.3</t>
-        </is>
-      </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Lit - AD risk</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>OpenTargets AD gene</t>
         </is>
       </c>
       <c r="E385" t="b">
+        <v>1</v>
+      </c>
+      <c r="F385" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>PSEN2</t>
+          <t>PSEN1</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E386" t="b">
@@ -10761,39 +11142,42 @@
           <t>PSEN2</t>
         </is>
       </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Glioblastoma_cancer</t>
+        </is>
+      </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Lit - AD risk</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>OpenTargets AD gene</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E387" t="b">
+        <v>1</v>
+      </c>
+      <c r="F387" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>PSENEN</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>Glioblastoma_cancer</t>
+          <t>PSEN2</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Lit - AD risk</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>OpenTargets AD gene</t>
         </is>
       </c>
       <c r="E388" t="b">
@@ -10806,12 +11190,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>PTCHD4</t>
+          <t>PSENEN</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Inhib.Lamp5</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -10821,7 +11205,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Lamp5</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E389" t="b">
@@ -10834,26 +11218,26 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>PTGDS</t>
+          <t>PTCHD4</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Astro.2</t>
+          <t>Inhib.Lamp5</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
+          <t>Base probe - Inhib.Lamp5</t>
         </is>
       </c>
       <c r="E390" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F390" t="b">
         <v>1</v>
@@ -10862,26 +11246,26 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>PTPRC</t>
+          <t>PTGDS</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Astro.2</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Astro.2 specific MR genes - Astro.2/Astro.5: 1.01, Astro.2 specific Enrich genes t= 4.92</t>
         </is>
       </c>
       <c r="E391" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F391" t="b">
         <v>1</v>
@@ -10895,20 +11279,23 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up logFC=3.24</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E392" t="b">
+        <v>1</v>
+      </c>
+      <c r="F392" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10920,7 +11307,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Oligo.5</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -10930,10 +11317,13 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.5 up</t>
+          <t>DEG carrier included: Oligo.3 up, DEG carrier top: Oligo.3 up logFC=3.24</t>
         </is>
       </c>
       <c r="E393" t="b">
+        <v>1</v>
+      </c>
+      <c r="F393" t="b">
         <v>1</v>
       </c>
     </row>
@@ -10945,27 +11335,30 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo.5</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>DEG carrier top: Oligo.3 AA_up</t>
+          <t>DEG carrier included: Oligo.5 up</t>
         </is>
       </c>
       <c r="E394" t="b">
+        <v>1</v>
+      </c>
+      <c r="F394" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>PTPRD</t>
+          <t>PTPRC</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -10975,41 +11368,44 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>DEGs - LR</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
+          <t>DEG carrier top: Oligo.3 AA_up</t>
         </is>
       </c>
       <c r="E395" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F395" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>PTPRZ1</t>
+          <t>PTPRD</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEGs - LR</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>DEG LR interactions: IL1RAPL1 -&gt; PTPRD,NTRK3 -&gt; PTPRD</t>
         </is>
       </c>
       <c r="E396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F396" t="b">
         <v>1</v>
@@ -11018,12 +11414,12 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>PVALB</t>
+          <t>PTPRZ1</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11033,7 +11429,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E397" t="b">
@@ -11046,51 +11442,54 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>RABL2B</t>
+          <t>PVALB</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="E398" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F398" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>RASGRP1</t>
+          <t>RABL2B</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up-EA_down*</t>
         </is>
       </c>
       <c r="E399" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F399" t="b">
         <v>1</v>
@@ -11099,12 +11498,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>RELN</t>
+          <t>RASGRP1</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -11114,7 +11513,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E400" t="b">
@@ -11132,42 +11531,45 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>L2.3~Sp09D01</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>SpD marker from Lit</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E401" t="b">
+        <v>1</v>
+      </c>
+      <c r="F401" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>RFTN1</t>
+          <t>RELN</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>L2.3~Sp09D01</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>SpD marker from Lit</t>
         </is>
       </c>
       <c r="E402" t="b">
@@ -11185,42 +11587,45 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E403" t="b">
+        <v>1</v>
+      </c>
+      <c r="F403" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>RGS10</t>
+          <t>RFTN1</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E404" t="b">
@@ -11233,12 +11638,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>RGS16</t>
+          <t>RGS10</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Micro</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -11248,7 +11653,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>Base probe - Micro</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E405" t="b">
@@ -11261,12 +11666,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>RIT2</t>
+          <t>RGS16</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Excit.L5_ET</t>
+          <t>Micro</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -11276,7 +11681,7 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_ET</t>
+          <t>Base probe - Micro</t>
         </is>
       </c>
       <c r="E406" t="b">
@@ -11294,17 +11699,17 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2</t>
+          <t>Excit.L5_ET</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
+          <t>Base probe - Excit.L5_ET</t>
         </is>
       </c>
       <c r="E407" t="b">
@@ -11317,51 +11722,54 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>RNASE1</t>
+          <t>RIT2</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L2_5.2</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Excit.L2_5.2 specific MR gene - Excit.L2_5.2/Excit.L6_CT: 2.087</t>
         </is>
       </c>
       <c r="E408" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F408" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>RNASET2</t>
+          <t>RNASE1</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="E409" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F409" t="b">
         <v>1</v>
@@ -11375,42 +11783,45 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E410" t="b">
+        <v>1</v>
+      </c>
+      <c r="F410" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>RNF144B</t>
+          <t>RNASET2</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Vasc.Endo</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.Endo</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E411" t="b">
@@ -11423,12 +11834,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>RORB</t>
+          <t>RNF144B</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Vasc.Endo</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -11438,7 +11849,7 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>Base probe - Vasc.Endo</t>
         </is>
       </c>
       <c r="E412" t="b">
@@ -11456,17 +11867,17 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Excit.L5.1</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="E413" t="b">
@@ -11479,22 +11890,22 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ROS1</t>
+          <t>RORB</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Excit.L5.1</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b</t>
+          <t>Excit.L5.1 specific MR gene - Excit.L5.1/Excit.L2_5.1: 4.221</t>
         </is>
       </c>
       <c r="E414" t="b">
@@ -11517,15 +11928,18 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>globl MR genes -  Excit.L6b/Excit.L2: 5.636</t>
+          <t>Base probe - Excit.L6b</t>
         </is>
       </c>
       <c r="E415" t="b">
+        <v>1</v>
+      </c>
+      <c r="F415" t="b">
         <v>1</v>
       </c>
     </row>
@@ -11542,12 +11956,12 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Marker - cell type global</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
+          <t>globl MR genes -  Excit.L6b/Excit.L2: 5.636</t>
         </is>
       </c>
       <c r="E416" t="b">
@@ -11560,12 +11974,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>RPS27</t>
+          <t>ROS1</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -11575,11 +11989,11 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
+          <t>Excit.L6b specific MR gene - Excit.L6b/Excit.L2: 5.636</t>
         </is>
       </c>
       <c r="E417" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F417" t="b">
         <v>1</v>
@@ -11588,26 +12002,26 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>RSPO2</t>
+          <t>RPS27</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Astro.3 specific MR genes - Astro.3/Astro.2: 1.109</t>
         </is>
       </c>
       <c r="E418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F418" t="b">
         <v>1</v>
@@ -11621,17 +12035,17 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E419" t="b">
@@ -11644,22 +12058,22 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>RXFP1</t>
+          <t>RSPO2</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Excit.L5_IT</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_IT</t>
+          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.829</t>
         </is>
       </c>
       <c r="E420" t="b">
@@ -11672,12 +12086,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>RYR3</t>
+          <t>RXFP1</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Excit.L5_IT</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -11687,7 +12101,7 @@
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Base probe - Astro</t>
+          <t>Base probe - Excit.L5_IT</t>
         </is>
       </c>
       <c r="E421" t="b">
@@ -11700,12 +12114,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>S100A4</t>
+          <t>RYR3</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Glioblastoma_TME</t>
+          <t>Astro</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -11715,7 +12129,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_TME</t>
+          <t>Base probe - Astro</t>
         </is>
       </c>
       <c r="E422" t="b">
@@ -11728,12 +12142,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>SAMD5</t>
+          <t>S100A4</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Inhib.Pvalb</t>
+          <t>Glioblastoma_TME</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -11743,7 +12157,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pvalb</t>
+          <t>Base probe - Glioblastoma_TME</t>
         </is>
       </c>
       <c r="E423" t="b">
@@ -11756,12 +12170,12 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>SDK1</t>
+          <t>SAMD5</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>Inhib.Pvalb</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -11771,7 +12185,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - Inhib.Pvalb</t>
         </is>
       </c>
       <c r="E424" t="b">
@@ -11789,17 +12203,17 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="E425" t="b">
@@ -11812,51 +12226,54 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>SELENOP</t>
+          <t>SDK1</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3-</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L6_CT: 1.88</t>
         </is>
       </c>
       <c r="E426" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F426" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>SEMA5A</t>
+          <t>SELENOP</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>MOFA Oligo.3 Factor3-</t>
         </is>
       </c>
       <c r="E427" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F427" t="b">
         <v>1</v>
@@ -11865,26 +12282,26 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>SEMA6D</t>
+          <t>SEMA5A</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Oligo.1</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E428" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F428" t="b">
         <v>1</v>
@@ -11893,26 +12310,26 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>SERPINA3</t>
+          <t>SEMA6D</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Vasc.VLMC</t>
+          <t>Oligo.1</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Base probe - Vasc.VLMC</t>
+          <t>Oligo.1 specific MR genes - Oligo.1/Oligo.2: 1.179</t>
         </is>
       </c>
       <c r="E429" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F429" t="b">
         <v>1</v>
@@ -11921,12 +12338,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>SFRP2</t>
+          <t>SERPINA3</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Vasc.VLMC</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -11936,7 +12353,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Base probe - Vasc.VLMC</t>
         </is>
       </c>
       <c r="E430" t="b">
@@ -11949,51 +12366,54 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>SGSM3</t>
+          <t>SFRP2</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E431" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F431" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>SLC17A6</t>
+          <t>SGSM3</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Excit.L4_IT</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L4_IT</t>
+          <t>DEG Ancestry op: Oligo.3 AA_up*-EA_down</t>
         </is>
       </c>
       <c r="E432" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F432" t="b">
         <v>1</v>
@@ -12007,17 +12427,17 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L4_IT</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
+          <t>Base probe - Excit.L4_IT</t>
         </is>
       </c>
       <c r="E433" t="b">
@@ -12030,22 +12450,22 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>SLC17A7</t>
+          <t>SLC17A6</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Excit.L6b</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6b</t>
+          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2: 1.542</t>
         </is>
       </c>
       <c r="E434" t="b">
@@ -12063,20 +12483,23 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6b</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Excit.L6b</t>
         </is>
       </c>
       <c r="E435" t="b">
+        <v>1</v>
+      </c>
+      <c r="F435" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12093,41 +12516,44 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E436" t="b">
+        <v>1</v>
+      </c>
+      <c r="F436" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SLC24A2</t>
+          <t>SLC17A7</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 8.18</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F437" t="b">
         <v>1</v>
@@ -12136,26 +12562,26 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>SLC24A3</t>
+          <t>SLC24A2</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip</t>
+          <t>Astro.3 specific Enrich genes t= 8.18</t>
         </is>
       </c>
       <c r="E438" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F438" t="b">
         <v>1</v>
@@ -12169,20 +12595,23 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 up</t>
+          <t>Base probe - Inhib.Vip</t>
         </is>
       </c>
       <c r="E439" t="b">
+        <v>1</v>
+      </c>
+      <c r="F439" t="b">
         <v>1</v>
       </c>
     </row>
@@ -12199,37 +12628,40 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>DEG - mediation</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>mediation gene: outcome Oligo.3</t>
+          <t>DEG carrier included: Oligo.3 up</t>
         </is>
       </c>
       <c r="E440" t="b">
+        <v>1</v>
+      </c>
+      <c r="F440" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>SLC26A4</t>
+          <t>SLC24A3</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - mediation</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>mediation gene: outcome Oligo.3</t>
         </is>
       </c>
       <c r="E441" t="b">
@@ -12242,52 +12674,58 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>SLC4A4</t>
+          <t>SLC26A4</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>MOFA - Factor3</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>MOFA Oligo.3 Factor3+</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E442" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F442" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>SLC5A11</t>
+          <t>SLC4A4</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Oligo.2</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Marker - cell type global</t>
+          <t>MOFA - Factor3</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>globl MR genes -  Oligo.2/Oligo.5: 1.492</t>
+          <t>MOFA Oligo.3 Factor3+</t>
         </is>
       </c>
       <c r="E443" t="b">
         <v>0</v>
       </c>
+      <c r="F443" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -12481,6 +12919,9 @@
       <c r="E450" t="b">
         <v>0</v>
       </c>
+      <c r="F450" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -12506,6 +12947,9 @@
       <c r="E451" t="b">
         <v>0</v>
       </c>
+      <c r="F451" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -12554,6 +12998,9 @@
       <c r="E453" t="b">
         <v>1</v>
       </c>
+      <c r="F453" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -12579,6 +13026,9 @@
       <c r="E454" t="b">
         <v>1</v>
       </c>
+      <c r="F454" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -12604,6 +13054,9 @@
       <c r="E455" t="b">
         <v>1</v>
       </c>
+      <c r="F455" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -12657,6 +13110,9 @@
       <c r="E457" t="b">
         <v>1</v>
       </c>
+      <c r="F457" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -12850,6 +13306,9 @@
       <c r="E464" t="b">
         <v>1</v>
       </c>
+      <c r="F464" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -12875,6 +13334,9 @@
       <c r="E465" t="b">
         <v>1</v>
       </c>
+      <c r="F465" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -13012,6 +13474,9 @@
       <c r="E470" t="b">
         <v>1</v>
       </c>
+      <c r="F470" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -13093,6 +13558,9 @@
       <c r="E473" t="b">
         <v>1</v>
       </c>
+      <c r="F473" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -13118,6 +13586,9 @@
       <c r="E474" t="b">
         <v>1</v>
       </c>
+      <c r="F474" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -13143,6 +13614,9 @@
       <c r="E475" t="b">
         <v>1</v>
       </c>
+      <c r="F475" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -13168,6 +13642,9 @@
       <c r="E476" t="b">
         <v>0</v>
       </c>
+      <c r="F476" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -13221,6 +13698,9 @@
       <c r="E478" t="b">
         <v>0</v>
       </c>
+      <c r="F478" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
@@ -13358,6 +13838,9 @@
       <c r="E483" t="b">
         <v>0</v>
       </c>
+      <c r="F483" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
@@ -13439,6 +13922,9 @@
       <c r="E486" t="b">
         <v>1</v>
       </c>
+      <c r="F486" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -13604,6 +14090,9 @@
       <c r="E492" t="b">
         <v>1</v>
       </c>
+      <c r="F492" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -13629,6 +14118,9 @@
       <c r="E493" t="b">
         <v>1</v>
       </c>
+      <c r="F493" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -13794,6 +14286,9 @@
       <c r="E499" t="b">
         <v>1</v>
       </c>
+      <c r="F499" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -13819,6 +14314,9 @@
       <c r="E500" t="b">
         <v>1</v>
       </c>
+      <c r="F500" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -13928,6 +14426,9 @@
       <c r="E504" t="b">
         <v>1</v>
       </c>
+      <c r="F504" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -13981,6 +14482,9 @@
       <c r="E506" t="b">
         <v>0</v>
       </c>
+      <c r="F506" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -14342,41 +14846,47 @@
       <c r="E519" t="b">
         <v>1</v>
       </c>
+      <c r="F519" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>TRIM51</t>
+          <t>TRPC5</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>WM.uf_Sp09D07-WM_Sp09D06</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>SpD pw gene t=7.53</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E520" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F520" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>TRPC5</t>
+          <t>TRPC6</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Excit.L6_IT_Car3</t>
+          <t>Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -14386,7 +14896,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
+          <t>Base probe - Inhib.Sst_Chold</t>
         </is>
       </c>
       <c r="E521" t="b">
@@ -14399,12 +14909,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>TRPC6</t>
+          <t>TSHZ2</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Inhib.Sst_Chold</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -14414,7 +14924,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Sst_Chold</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="E522" t="b">
@@ -14432,17 +14942,17 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Astro.4</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 4.669</t>
         </is>
       </c>
       <c r="E523" t="b">
@@ -14460,7 +14970,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Astro.4</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -14470,7 +14980,7 @@
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 4.669</t>
+          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
         </is>
       </c>
       <c r="E524" t="b">
@@ -14483,22 +14993,22 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>TSHZ2</t>
+          <t>TTYH1</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP specific MR gene - Excit.L5_6_NP/Excit.L5.1: 1.691</t>
+          <t>Base probe - Glioblastoma_cancer</t>
         </is>
       </c>
       <c r="E525" t="b">
@@ -14516,17 +15026,17 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Glioblastoma_cancer</t>
+          <t>L1~Sp09D05</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - SpD</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Base probe - Glioblastoma_cancer</t>
+          <t>SpD Enrich gene t=13.38</t>
         </is>
       </c>
       <c r="E526" t="b">
@@ -14539,51 +15049,57 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>TTYH1</t>
+          <t>UBXN2A</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>L1~Sp09D05</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Marker - SpD</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>SpD Enrich gene t=13.38</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="E527" t="b">
+        <v>0</v>
+      </c>
+      <c r="F527" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>UBXN2A</t>
+          <t>UGT8</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Oligo</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Oligo</t>
         </is>
       </c>
       <c r="E528" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F528" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -14594,17 +15110,17 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Oligo</t>
+          <t>Astro.3</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Base probe - Oligo</t>
+          <t>Astro.3 specific Enrich genes t= 7.67</t>
         </is>
       </c>
       <c r="E529" t="b">
@@ -14627,12 +15143,12 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Astro.3 specific Enrich genes t= 7.67</t>
+          <t>DEG carrier included: Astro.3 down</t>
         </is>
       </c>
       <c r="E530" t="b">
@@ -14650,7 +15166,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>Astro.3</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -14660,47 +15176,53 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>DEG carrier included: Astro.3 down</t>
+          <t>DEG carrier included: Oligo.3 down</t>
         </is>
       </c>
       <c r="E531" t="b">
+        <v>1</v>
+      </c>
+      <c r="F531" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>UGT8</t>
+          <t>UNC5B</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Inhib.Chandelier</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>DEG carrier included: Oligo.3 down</t>
+          <t>Base probe - Inhib.Chandelier</t>
         </is>
       </c>
       <c r="E532" t="b">
+        <v>1</v>
+      </c>
+      <c r="F532" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>UNC5B</t>
+          <t>VCAN</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Inhib.Chandelier</t>
+          <t>OPC</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -14710,7 +15232,7 @@
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Chandelier</t>
+          <t>Base probe - OPC</t>
         </is>
       </c>
       <c r="E533" t="b">
@@ -14728,17 +15250,17 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>OPC</t>
+          <t>Astro.4</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Base probe - OPC</t>
+          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
         </is>
       </c>
       <c r="E534" t="b">
@@ -14751,22 +15273,22 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>VCAN</t>
+          <t>VIP</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Astro.4</t>
+          <t>Inhib.Vip</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Astro.4 specific MR gene - Astro.4/Astro.5: 3.185</t>
+          <t>Base probe - Inhib.Vip</t>
         </is>
       </c>
       <c r="E535" t="b">
@@ -14779,26 +15301,26 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>VIP</t>
+          <t>VPS54</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Inhib.Vip</t>
+          <t>Oligo.3</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - ancestry</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Vip</t>
+          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
         </is>
       </c>
       <c r="E536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F536" t="b">
         <v>1</v>
@@ -14807,26 +15329,29 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>VPS54</t>
+          <t>VWC2L</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Oligo.3</t>
+          <t>Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>DEG - ancestry</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>DEG Ancestry op: Oligo.3 AA_down*-EA_up</t>
+          <t>Base probe - Excit.L5_6_NP</t>
         </is>
       </c>
       <c r="E537" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F537" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -14837,17 +15362,17 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Excit.L5_6_NP</t>
+          <t>Excit.L2_5.2</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L5_6_NP</t>
+          <t>DEG carrier included: Excit.L2_5.2 up</t>
         </is>
       </c>
       <c r="E538" t="b">
@@ -14860,25 +15385,28 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>VWC2L</t>
+          <t>WIF1</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Excit.L2_5.2</t>
+          <t>Inhib.Pax6</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>DEG carrier included: Excit.L2_5.2 up</t>
+          <t>Base probe - Inhib.Pax6</t>
         </is>
       </c>
       <c r="E539" t="b">
+        <v>1</v>
+      </c>
+      <c r="F539" t="b">
         <v>1</v>
       </c>
     </row>
@@ -14890,17 +15418,17 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Inhib.Pax6</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Marker - cell type specific</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Base probe - Inhib.Pax6</t>
+          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
         </is>
       </c>
       <c r="E540" t="b">
@@ -14913,22 +15441,22 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>WIF1</t>
+          <t>ZBBX</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Marker - cell type specific</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Excit.L5.2 specific MR gene - Excit.L5.2/Excit.L2_5.2: 1.998</t>
+          <t>Base probe - Excit.L2_3_IT</t>
         </is>
       </c>
       <c r="E541" t="b">
@@ -14941,26 +15469,26 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>ZBBX</t>
+          <t>ZDHHC11</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Excit.L2_3_IT</t>
+          <t>Excit.L5.2</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>DEG - carrier</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>Base probe - Excit.L2_3_IT</t>
+          <t>DEG carrier top: Excit.L5.2 down</t>
         </is>
       </c>
       <c r="E542" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F542" t="b">
         <v>1</v>
@@ -14969,53 +15497,28 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>ZDHHC11</t>
+          <t>ZDHHC23</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Excit.L5.2</t>
+          <t>Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>DEG - carrier</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>DEG carrier top:  Excit.L5.2 down</t>
+          <t>Base probe - Excit.L6_IT_Car3</t>
         </is>
       </c>
       <c r="E543" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>ZDHHC23</t>
-        </is>
-      </c>
-      <c r="B544" t="inlineStr">
-        <is>
-          <t>Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>Base probe - Excit.L6_IT_Car3</t>
-        </is>
-      </c>
-      <c r="E544" t="b">
-        <v>1</v>
-      </c>
-      <c r="F544" t="b">
+        <v>1</v>
+      </c>
+      <c r="F543" t="b">
         <v>1</v>
       </c>
     </row>
